--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2019/ALASKA_2019.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2019/ALASKA_2019.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D85"/>
+  <dimension ref="A1:D79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Total</t>
@@ -426,6 +431,11 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>Mexicali</t>
@@ -439,6 +449,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Tijuana</t>
@@ -452,6 +467,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Total</t>
@@ -483,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Delicias</t>
@@ -496,6 +521,11 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>Juárez</t>
@@ -509,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Total</t>
@@ -540,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Total</t>
@@ -555,7 +595,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -571,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -584,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Iztacalco</t>
@@ -597,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -610,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Total</t>
@@ -641,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Total</t>
@@ -672,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>León</t>
@@ -685,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Total</t>
@@ -716,9 +791,14 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tlapa de Comonfort</t>
+          <t>Tlapa De Comonfort</t>
         </is>
       </c>
       <c r="C25">
@@ -729,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Total</t>
@@ -749,7 +834,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cuautepec de Hinojosa</t>
+          <t>Cuautepec De Hinojosa</t>
         </is>
       </c>
       <c r="C27">
@@ -760,9 +845,14 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tulancingo de Bravo</t>
+          <t>Tulancingo De Bravo</t>
         </is>
       </c>
       <c r="C28">
@@ -773,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Total</t>
@@ -804,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Jalostotitlán</t>
@@ -817,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Ocotlán</t>
@@ -830,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Pihuamo</t>
@@ -843,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Puerto Vallarta</t>
@@ -856,9 +971,14 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>San Juan de los Lagos</t>
+          <t>San Juan De Los Lagos</t>
         </is>
       </c>
       <c r="C35">
@@ -869,9 +989,14 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>San Miguel el Alto</t>
+          <t>San Miguel El Alto</t>
         </is>
       </c>
       <c r="C36">
@@ -882,9 +1007,14 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tepatitlán de Morelos</t>
+          <t>Tepatitlán De Morelos</t>
         </is>
       </c>
       <c r="C37">
@@ -895,6 +1025,11 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>Tequila</t>
@@ -908,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>San Pedro Tlaquepaque</t>
@@ -921,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -934,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Total</t>
@@ -965,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Carácuaro</t>
@@ -978,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Charo</t>
@@ -991,6 +1151,11 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>Huetamo</t>
@@ -1004,6 +1169,11 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>Indaparapeo</t>
@@ -1017,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Jungapeo</t>
@@ -1030,6 +1205,11 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Morelia</t>
@@ -1043,6 +1223,11 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -1056,6 +1241,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>Zacapu</t>
@@ -1069,6 +1259,11 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>Zamora</t>
@@ -1082,6 +1277,11 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1102,7 +1302,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ixtlán del Río</t>
+          <t>Ixtlán Del Río</t>
         </is>
       </c>
       <c r="C53">
@@ -1113,6 +1313,11 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>Santiago Ixcuintla</t>
@@ -1126,6 +1331,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1146,7 +1356,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>San Nicolás de los Garza</t>
+          <t>San Nicolás De Los Garza</t>
         </is>
       </c>
       <c r="C56">
@@ -1157,6 +1367,11 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1177,7 +1392,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Miahuatlán de Porfirio Díaz</t>
+          <t>Miahuatlán De Porfirio Díaz</t>
         </is>
       </c>
       <c r="C58">
@@ -1188,6 +1403,11 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>Santiago Juxtlahuaca</t>
@@ -1201,6 +1421,11 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>Santo Domingo Tehuantepec</t>
@@ -1214,6 +1439,11 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>Silacayoápam</t>
@@ -1227,6 +1457,11 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1258,6 +1493,11 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1289,6 +1529,11 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1320,6 +1565,11 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1351,6 +1601,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>Hidalgotitlán</t>
@@ -1364,6 +1619,11 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>Papantla</t>
@@ -1377,6 +1637,11 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>Tierra Blanca</t>
@@ -1390,6 +1655,11 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1421,6 +1691,11 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -1434,9 +1709,14 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Tlaltenango de Sánchez Román</t>
+          <t>Tlaltenango De Sánchez Román</t>
         </is>
       </c>
       <c r="C76">
@@ -1447,6 +1727,11 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>Zacatecas</t>
@@ -1460,6 +1745,11 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1483,41 +1773,6 @@
       </c>
       <c r="D79">
         <v>1</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 800,811</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Abril de 2020</t>
-        </is>
       </c>
     </row>
   </sheetData>
